--- a/ProjectC/Assets/Excel/CardData.xlsx
+++ b/ProjectC/Assets/Excel/CardData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="205">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,13 +62,6 @@
   </si>
   <si>
     <t>Magic</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Card Type</t>
@@ -249,12 +242,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Murloc</t>
-  </si>
-  <si>
-    <t>Beast</t>
-  </si>
-  <si>
     <t>Novice_Engineer</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -311,9 +298,6 @@
   <si>
     <t>Magma_Rager</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Element</t>
   </si>
   <si>
     <t>공격대장</t>
@@ -364,10 +348,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Neutral</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>은빛털고릴라 우두머리</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -594,16 +574,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Druid</t>
-  </si>
-  <si>
     <t>Magic Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Nature</t>
-  </si>
-  <si>
     <t>Innervate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -618,9 +592,6 @@
   <si>
     <t>피해를 1 줍니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Arcane</t>
   </si>
   <si>
     <t>Claw</t>
@@ -742,9 +713,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hunter</t>
-  </si>
-  <si>
     <t>회갈색 늑대</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -870,12 +838,44 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,2,3,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mech</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>중립</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>드루이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사냥꾼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야수</t>
+  </si>
+  <si>
+    <t>야수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정령</t>
+  </si>
+  <si>
+    <t>자연</t>
+  </si>
+  <si>
+    <t>비전</t>
   </si>
 </sst>
 </file>
@@ -1254,31 +1254,31 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="49.5" x14ac:dyDescent="0.3">
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1298,28 +1298,25 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>205</v>
-      </c>
-      <c r="N2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -1327,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1339,25 +1336,25 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="K3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="49.5" x14ac:dyDescent="0.3">
@@ -1365,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1377,25 +1374,25 @@
         <v>1</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
@@ -1403,7 +1400,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1415,22 +1412,22 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" t="s">
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L5" t="s">
-        <v>56</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -1438,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1450,25 +1447,25 @@
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
         <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="66" x14ac:dyDescent="0.3">
@@ -1476,7 +1473,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1488,25 +1485,25 @@
         <v>1</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" t="s">
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="66" x14ac:dyDescent="0.3">
@@ -1514,7 +1511,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -1526,25 +1523,25 @@
         <v>2</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -1552,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -1564,22 +1561,22 @@
         <v>2</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I9" t="s">
         <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L9" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -1587,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -1599,25 +1596,25 @@
         <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
       </c>
       <c r="J10" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L10" t="s">
-        <v>56</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -1625,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -1637,25 +1634,25 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -1663,7 +1660,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -1675,25 +1672,25 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I12" t="s">
         <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -1701,7 +1698,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -1713,25 +1710,25 @@
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I13" t="s">
         <v>8</v>
       </c>
       <c r="J13" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L13" t="s">
-        <v>56</v>
+        <v>198</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -1742,7 +1739,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1754,25 +1751,25 @@
         <v>1</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
         <v>8</v>
       </c>
       <c r="J14" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K14" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -1780,7 +1777,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1792,22 +1789,22 @@
         <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I15" t="s">
         <v>8</v>
       </c>
       <c r="J15" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L15" t="s">
-        <v>57</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -1815,7 +1812,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -1827,25 +1824,25 @@
         <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
         <v>8</v>
       </c>
       <c r="J16" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -1853,7 +1850,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -1865,25 +1862,25 @@
         <v>2</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I17" t="s">
         <v>8</v>
       </c>
       <c r="J17" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1891,7 +1888,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -1903,25 +1900,25 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I18" t="s">
         <v>8</v>
       </c>
       <c r="J18" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L18" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1929,7 +1926,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -1941,22 +1938,22 @@
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I19" t="s">
         <v>8</v>
       </c>
       <c r="J19" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L19" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1964,7 +1961,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -1976,25 +1973,25 @@
         <v>2</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I20" t="s">
         <v>8</v>
       </c>
       <c r="J20" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="66" x14ac:dyDescent="0.3">
@@ -2002,7 +1999,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2014,25 +2011,25 @@
         <v>3</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I21" t="s">
         <v>8</v>
       </c>
       <c r="J21" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N21">
         <v>2</v>
@@ -2043,7 +2040,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2055,25 +2052,25 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I22" t="s">
         <v>8</v>
       </c>
       <c r="J22" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
       <c r="K22" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -2081,7 +2078,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2093,25 +2090,25 @@
         <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s">
         <v>8</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L23" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2119,7 +2116,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2131,25 +2128,25 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s">
         <v>8</v>
       </c>
       <c r="J24" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L24" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2157,7 +2154,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2169,22 +2166,22 @@
         <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s">
         <v>8</v>
       </c>
       <c r="J25" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -2192,7 +2189,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -2204,25 +2201,25 @@
         <v>4</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I26" t="s">
         <v>8</v>
       </c>
       <c r="J26" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N26">
         <v>3</v>
@@ -2233,7 +2230,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -2245,25 +2242,25 @@
         <v>4</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I27" t="s">
         <v>8</v>
       </c>
       <c r="J27" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K27" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2271,7 +2268,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -2283,22 +2280,22 @@
         <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s">
         <v>8</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2306,7 +2303,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -2318,25 +2315,25 @@
         <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s">
         <v>8</v>
       </c>
       <c r="J29" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K29" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L29" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2344,7 +2341,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -2356,25 +2353,25 @@
         <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I30" t="s">
         <v>8</v>
       </c>
       <c r="J30" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2382,7 +2379,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -2394,25 +2391,25 @@
         <v>5</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I31" t="s">
         <v>8</v>
       </c>
       <c r="J31" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2420,7 +2417,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -2432,25 +2429,25 @@
         <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s">
         <v>8</v>
       </c>
       <c r="J32" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
@@ -2458,7 +2455,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -2470,25 +2467,25 @@
         <v>5</v>
       </c>
       <c r="F33" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s">
         <v>8</v>
       </c>
       <c r="J33" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K33" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="66" x14ac:dyDescent="0.3">
@@ -2496,7 +2493,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -2508,25 +2505,25 @@
         <v>4</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I34" t="s">
         <v>8</v>
       </c>
       <c r="J34" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K34" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="66" x14ac:dyDescent="0.3">
@@ -2534,7 +2531,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -2546,25 +2543,25 @@
         <v>7</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I35" t="s">
         <v>8</v>
       </c>
       <c r="J35" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K35" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
@@ -2572,7 +2569,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -2584,25 +2581,25 @@
         <v>4</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="H36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I36" t="s">
         <v>8</v>
       </c>
       <c r="J36" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L36" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
@@ -2610,7 +2607,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -2622,25 +2619,25 @@
         <v>2</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="H37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I37" t="s">
         <v>8</v>
       </c>
       <c r="J37" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K37" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="33" x14ac:dyDescent="0.3">
@@ -2648,7 +2645,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -2660,25 +2657,25 @@
         <v>7</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I38" t="s">
         <v>8</v>
       </c>
       <c r="J38" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K38" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -2686,7 +2683,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C39">
         <v>6</v>
@@ -2698,22 +2695,22 @@
         <v>7</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I39" t="s">
         <v>8</v>
       </c>
       <c r="J39" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -2721,7 +2718,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C40">
         <v>6</v>
@@ -2733,25 +2730,25 @@
         <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I40" t="s">
         <v>8</v>
       </c>
       <c r="J40" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
@@ -2759,7 +2756,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -2771,25 +2768,25 @@
         <v>2</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I41" t="s">
         <v>8</v>
       </c>
       <c r="J41" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
@@ -2797,7 +2794,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C42">
         <v>7</v>
@@ -2809,22 +2806,22 @@
         <v>5</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I42" t="s">
         <v>8</v>
       </c>
       <c r="J42" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L42" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="33" x14ac:dyDescent="0.3">
@@ -2832,7 +2829,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C43">
         <v>7</v>
@@ -2844,25 +2841,25 @@
         <v>6</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I43" t="s">
         <v>8</v>
       </c>
       <c r="J43" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K43" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
@@ -2870,7 +2867,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C44">
         <v>7</v>
@@ -2882,22 +2879,22 @@
         <v>7</v>
       </c>
       <c r="G44" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I44" t="s">
         <v>8</v>
       </c>
       <c r="J44" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="K44" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="49.5" x14ac:dyDescent="0.3">
@@ -2905,31 +2902,31 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I45" t="s">
         <v>9</v>
       </c>
       <c r="J45" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M45" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
@@ -2937,31 +2934,31 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="F46" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I46" t="s">
         <v>9</v>
       </c>
       <c r="J46" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M46" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="66" x14ac:dyDescent="0.3">
@@ -2969,31 +2966,31 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I47" t="s">
         <v>9</v>
       </c>
       <c r="J47" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="66" x14ac:dyDescent="0.3">
@@ -3001,31 +2998,31 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="H48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I48" t="s">
         <v>9</v>
       </c>
       <c r="J48" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M48" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="33" x14ac:dyDescent="0.3">
@@ -3033,31 +3030,31 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="H49" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I49" t="s">
         <v>9</v>
       </c>
       <c r="J49" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M49" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="66" x14ac:dyDescent="0.3">
@@ -3065,31 +3062,31 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I50" t="s">
         <v>9</v>
       </c>
       <c r="J50" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M50" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="33" x14ac:dyDescent="0.3">
@@ -3097,31 +3094,31 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C51">
         <v>2</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I51" t="s">
         <v>9</v>
       </c>
       <c r="J51" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M51" t="s">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="N51">
         <v>4</v>
@@ -3132,31 +3129,31 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C52">
         <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="H52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I52" t="s">
         <v>9</v>
       </c>
       <c r="J52" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K52" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M52" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="33" x14ac:dyDescent="0.3">
@@ -3164,31 +3161,31 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C53">
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="H53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I53" t="s">
         <v>9</v>
       </c>
       <c r="J53" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M53" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -3196,7 +3193,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C54">
         <v>8</v>
@@ -3208,25 +3205,25 @@
         <v>8</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I54" t="s">
         <v>8</v>
       </c>
       <c r="J54" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="K54" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>72</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -3234,31 +3231,31 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I55" t="s">
         <v>9</v>
       </c>
       <c r="J55" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K55" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M55" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3266,7 +3263,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -3278,25 +3275,25 @@
         <v>1</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="H56" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I56" t="s">
         <v>8</v>
       </c>
       <c r="J56" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K56" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3304,31 +3301,31 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="H57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I57" t="s">
         <v>9</v>
       </c>
       <c r="J57" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M57" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3336,31 +3333,31 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C58">
         <v>1</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="H58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I58" t="s">
         <v>9</v>
       </c>
       <c r="J58" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K58" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M58" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3368,34 +3365,34 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I59" t="s">
         <v>9</v>
       </c>
       <c r="J59" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N59" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="66" x14ac:dyDescent="0.3">
@@ -3403,31 +3400,31 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="H60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I60" t="s">
         <v>9</v>
       </c>
       <c r="J60" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K60" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="82.5" x14ac:dyDescent="0.3">
@@ -3435,7 +3432,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C61">
         <v>4</v>
@@ -3447,25 +3444,25 @@
         <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I61" t="s">
         <v>8</v>
       </c>
       <c r="J61" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K61" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3473,31 +3470,31 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C62">
         <v>4</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="G62" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I62" t="s">
         <v>9</v>
       </c>
       <c r="J62" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K62" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3505,7 +3502,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -3517,25 +3514,25 @@
         <v>1</v>
       </c>
       <c r="F63" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H63" t="s">
+        <v>40</v>
+      </c>
+      <c r="I63" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" t="s">
+        <v>196</v>
+      </c>
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" t="s">
         <v>199</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="H63" t="s">
-        <v>42</v>
-      </c>
-      <c r="I63" t="s">
-        <v>8</v>
-      </c>
-      <c r="J63" t="s">
-        <v>175</v>
-      </c>
-      <c r="K63" t="s">
-        <v>17</v>
-      </c>
-      <c r="L63" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="49.5" x14ac:dyDescent="0.3">
@@ -3543,7 +3540,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C64">
         <v>5</v>
@@ -3555,38 +3552,32 @@
         <v>5</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H64" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I64" t="s">
         <v>8</v>
       </c>
       <c r="J64" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K64" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576">
-      <formula1>"Murloc,Beast,None,Element,Mech,Dragon"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>"Minion,Magic"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J1048576">
-      <formula1>"Warrior,Prist,Hunter,Mage,Druid,Mage,Paladin,Rogue,Shaman,Neutral"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K1048576">
       <formula1>"Original,Other"</formula1>
@@ -3595,7 +3586,13 @@
       <formula1>"Gem_Common,Gem_Rare,Gem_Epic,Gem_Legendary,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M1:M1048576">
-      <formula1>"Nature,Arcane,Fire,Frost,Holy,Shadow,None"</formula1>
+      <formula1>"자연,비전,화염,냉기,신성,암흑,None"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
+      <formula1>"전사,사제,사냥꾼,드루이드,마법사,성기사,도적,주술사,중립"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576">
+      <formula1>"멀록,야수,None,정령,기계,용족"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ProjectC/Assets/Excel/CardData.xlsx
+++ b/ProjectC/Assets/Excel/CardData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="284">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -876,6 +876,316 @@
   </si>
   <si>
     <t>비전</t>
+  </si>
+  <si>
+    <t>마법사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arcane_Missiles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror_Image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arcane_Explosion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frostbolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arcane_Intellect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frost_Nova</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Original</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fireball</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Polymorph</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water_Elemental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정령</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flamestrike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blessing_of_Might</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성기사</t>
+  </si>
+  <si>
+    <t>Hand_of_Protection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Humility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light's_Justice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Holy_Light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blessing_of_Kings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Consecration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hammer_of_Wrath</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Truesilver_Champion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Guardian_of_Kings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Holy_Smite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사제</t>
+  </si>
+  <si>
+    <t>Mind_Vision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power_Word-_Shield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shadow_Word-_Pain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shadow_Word-_Death</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Holy_Nova</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mind_Control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Backstab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>도적</t>
+  </si>
+  <si>
+    <t>Deadly_Poison</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sinister_Strike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fan_of_Knives</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assassin's_Blade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assassinate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sprint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ancestral_Healing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주술사</t>
+  </si>
+  <si>
+    <t>Totemic_Might</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frost_Shock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rockbiter_Weapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flametongue_Totem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windfury</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windspeaker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bloodlust</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주술사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire_Elemental</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sacrificial_Pact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흑마법사</t>
+  </si>
+  <si>
+    <t>Soulfire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Corruption</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mortal_Coil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voidwalker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Felstalker</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drain_Life</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shadow_Bolt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hellfire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dread_Infernal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Execute</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전사</t>
+  </si>
+  <si>
+    <t>전사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Whirlwind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cleave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fiery_War_Axe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heroic_Strike</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shield_Block</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Warsong_Commander</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kor'kron_Elite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Arcanite_Reaper</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1214,7 +1524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.875" customWidth="1"/>
@@ -3573,6 +3883,1534 @@
         <v>199</v>
       </c>
     </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="H65" t="s">
+        <v>40</v>
+      </c>
+      <c r="I65" t="s">
+        <v>9</v>
+      </c>
+      <c r="J65" t="s">
+        <v>205</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" t="s">
+        <v>40</v>
+      </c>
+      <c r="I66" t="s">
+        <v>210</v>
+      </c>
+      <c r="J66" t="s">
+        <v>205</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="C67">
+        <v>2</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" t="s">
+        <v>40</v>
+      </c>
+      <c r="I67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67" t="s">
+        <v>205</v>
+      </c>
+      <c r="K67" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H68" t="s">
+        <v>40</v>
+      </c>
+      <c r="I68" t="s">
+        <v>9</v>
+      </c>
+      <c r="J68" t="s">
+        <v>205</v>
+      </c>
+      <c r="K68" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H69" t="s">
+        <v>40</v>
+      </c>
+      <c r="I69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69" t="s">
+        <v>205</v>
+      </c>
+      <c r="K69" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H70" t="s">
+        <v>40</v>
+      </c>
+      <c r="I70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J70" t="s">
+        <v>205</v>
+      </c>
+      <c r="K70" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="C71">
+        <v>4</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H71" t="s">
+        <v>40</v>
+      </c>
+      <c r="I71" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" t="s">
+        <v>205</v>
+      </c>
+      <c r="K71" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="C72">
+        <v>4</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H72" t="s">
+        <v>40</v>
+      </c>
+      <c r="I72" t="s">
+        <v>9</v>
+      </c>
+      <c r="J72" t="s">
+        <v>205</v>
+      </c>
+      <c r="K72" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="C73">
+        <v>4</v>
+      </c>
+      <c r="D73">
+        <v>3</v>
+      </c>
+      <c r="E73">
+        <v>6</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H73" t="s">
+        <v>40</v>
+      </c>
+      <c r="I73" t="s">
+        <v>8</v>
+      </c>
+      <c r="J73" t="s">
+        <v>205</v>
+      </c>
+      <c r="K73" t="s">
+        <v>15</v>
+      </c>
+      <c r="L73" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="C74">
+        <v>7</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H74" t="s">
+        <v>40</v>
+      </c>
+      <c r="I74" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" t="s">
+        <v>205</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H75" t="s">
+        <v>40</v>
+      </c>
+      <c r="I75" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" t="s">
+        <v>220</v>
+      </c>
+      <c r="K75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H76" t="s">
+        <v>40</v>
+      </c>
+      <c r="I76" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" t="s">
+        <v>220</v>
+      </c>
+      <c r="K76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="H77" t="s">
+        <v>40</v>
+      </c>
+      <c r="I77" t="s">
+        <v>9</v>
+      </c>
+      <c r="J77" t="s">
+        <v>220</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H78" t="s">
+        <v>40</v>
+      </c>
+      <c r="J78" t="s">
+        <v>220</v>
+      </c>
+      <c r="K78" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H79" t="s">
+        <v>40</v>
+      </c>
+      <c r="I79" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" t="s">
+        <v>220</v>
+      </c>
+      <c r="K79" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="H80" t="s">
+        <v>40</v>
+      </c>
+      <c r="I80" t="s">
+        <v>210</v>
+      </c>
+      <c r="J80" t="s">
+        <v>220</v>
+      </c>
+      <c r="K80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="C81">
+        <v>4</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H81" t="s">
+        <v>40</v>
+      </c>
+      <c r="I81" t="s">
+        <v>210</v>
+      </c>
+      <c r="J81" t="s">
+        <v>220</v>
+      </c>
+      <c r="K81" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="C82">
+        <v>4</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H82" t="s">
+        <v>40</v>
+      </c>
+      <c r="I82" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" t="s">
+        <v>220</v>
+      </c>
+      <c r="K82" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="C83">
+        <v>4</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H83" t="s">
+        <v>40</v>
+      </c>
+      <c r="J83" t="s">
+        <v>220</v>
+      </c>
+      <c r="K83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="H84" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" t="s">
+        <v>8</v>
+      </c>
+      <c r="J84" t="s">
+        <v>220</v>
+      </c>
+      <c r="K84" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H85" t="s">
+        <v>40</v>
+      </c>
+      <c r="I85" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85" t="s">
+        <v>231</v>
+      </c>
+      <c r="K85" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>84</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H86" t="s">
+        <v>40</v>
+      </c>
+      <c r="I86" t="s">
+        <v>210</v>
+      </c>
+      <c r="J86" t="s">
+        <v>231</v>
+      </c>
+      <c r="K86" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>85</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H87" t="s">
+        <v>40</v>
+      </c>
+      <c r="I87" t="s">
+        <v>210</v>
+      </c>
+      <c r="J87" t="s">
+        <v>231</v>
+      </c>
+      <c r="K87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>86</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H88" t="s">
+        <v>237</v>
+      </c>
+      <c r="I88" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" t="s">
+        <v>231</v>
+      </c>
+      <c r="K88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>87</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H89" t="s">
+        <v>40</v>
+      </c>
+      <c r="I89" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" t="s">
+        <v>231</v>
+      </c>
+      <c r="K89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>88</v>
+      </c>
+      <c r="C90">
+        <v>5</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="H90" t="s">
+        <v>40</v>
+      </c>
+      <c r="I90" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" t="s">
+        <v>231</v>
+      </c>
+      <c r="K90" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>89</v>
+      </c>
+      <c r="C91">
+        <v>10</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H91" t="s">
+        <v>40</v>
+      </c>
+      <c r="I91" t="s">
+        <v>9</v>
+      </c>
+      <c r="J91" t="s">
+        <v>231</v>
+      </c>
+      <c r="K91" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>90</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H92" t="s">
+        <v>40</v>
+      </c>
+      <c r="I92" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" t="s">
+        <v>240</v>
+      </c>
+      <c r="K92" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>91</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H93" t="s">
+        <v>40</v>
+      </c>
+      <c r="I93" t="s">
+        <v>9</v>
+      </c>
+      <c r="J93" t="s">
+        <v>240</v>
+      </c>
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>92</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="H94" t="s">
+        <v>40</v>
+      </c>
+      <c r="I94" t="s">
+        <v>210</v>
+      </c>
+      <c r="J94" t="s">
+        <v>240</v>
+      </c>
+      <c r="K94" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>93</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H95" t="s">
+        <v>40</v>
+      </c>
+      <c r="I95" t="s">
+        <v>210</v>
+      </c>
+      <c r="J95" t="s">
+        <v>240</v>
+      </c>
+      <c r="K95" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>94</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H96" t="s">
+        <v>40</v>
+      </c>
+      <c r="I96" t="s">
+        <v>210</v>
+      </c>
+      <c r="J96" t="s">
+        <v>240</v>
+      </c>
+      <c r="K96" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>95</v>
+      </c>
+      <c r="C97">
+        <v>5</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H97" t="s">
+        <v>40</v>
+      </c>
+      <c r="J97" t="s">
+        <v>240</v>
+      </c>
+      <c r="K97" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>96</v>
+      </c>
+      <c r="C98">
+        <v>5</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H98" t="s">
+        <v>40</v>
+      </c>
+      <c r="I98" t="s">
+        <v>9</v>
+      </c>
+      <c r="J98" t="s">
+        <v>240</v>
+      </c>
+      <c r="K98" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>97</v>
+      </c>
+      <c r="C99">
+        <v>7</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H99" t="s">
+        <v>40</v>
+      </c>
+      <c r="I99" t="s">
+        <v>9</v>
+      </c>
+      <c r="J99" t="s">
+        <v>240</v>
+      </c>
+      <c r="K99" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>98</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H100" t="s">
+        <v>40</v>
+      </c>
+      <c r="I100" t="s">
+        <v>9</v>
+      </c>
+      <c r="J100" t="s">
+        <v>249</v>
+      </c>
+      <c r="K100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>99</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H101" t="s">
+        <v>40</v>
+      </c>
+      <c r="I101" t="s">
+        <v>9</v>
+      </c>
+      <c r="J101" t="s">
+        <v>249</v>
+      </c>
+      <c r="K101" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>100</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H102" t="s">
+        <v>40</v>
+      </c>
+      <c r="I102" t="s">
+        <v>9</v>
+      </c>
+      <c r="J102" t="s">
+        <v>249</v>
+      </c>
+      <c r="K102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>101</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="H103" t="s">
+        <v>40</v>
+      </c>
+      <c r="I103" t="s">
+        <v>9</v>
+      </c>
+      <c r="J103" t="s">
+        <v>249</v>
+      </c>
+      <c r="K103" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>102</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H104" t="s">
+        <v>40</v>
+      </c>
+      <c r="I104" t="s">
+        <v>254</v>
+      </c>
+      <c r="J104" t="s">
+        <v>249</v>
+      </c>
+      <c r="K104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>103</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H105" t="s">
+        <v>40</v>
+      </c>
+      <c r="I105" t="s">
+        <v>9</v>
+      </c>
+      <c r="J105" t="s">
+        <v>259</v>
+      </c>
+      <c r="K105" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>104</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H106" t="s">
+        <v>40</v>
+      </c>
+      <c r="I106" t="s">
+        <v>210</v>
+      </c>
+      <c r="J106" t="s">
+        <v>249</v>
+      </c>
+      <c r="K106" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>105</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H107" t="s">
+        <v>40</v>
+      </c>
+      <c r="I107" t="s">
+        <v>8</v>
+      </c>
+      <c r="J107" t="s">
+        <v>249</v>
+      </c>
+      <c r="K107" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>106</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H108" t="s">
+        <v>40</v>
+      </c>
+      <c r="I108" t="s">
+        <v>9</v>
+      </c>
+      <c r="J108" t="s">
+        <v>249</v>
+      </c>
+      <c r="K108" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>107</v>
+      </c>
+      <c r="C109">
+        <v>6</v>
+      </c>
+      <c r="D109">
+        <v>6</v>
+      </c>
+      <c r="E109">
+        <v>5</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H109" t="s">
+        <v>40</v>
+      </c>
+      <c r="I109" t="s">
+        <v>8</v>
+      </c>
+      <c r="J109" t="s">
+        <v>249</v>
+      </c>
+      <c r="K109" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>108</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="H110" t="s">
+        <v>40</v>
+      </c>
+      <c r="I110" t="s">
+        <v>9</v>
+      </c>
+      <c r="J110" t="s">
+        <v>262</v>
+      </c>
+      <c r="K110" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>109</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H111" t="s">
+        <v>40</v>
+      </c>
+      <c r="I111" t="s">
+        <v>210</v>
+      </c>
+      <c r="J111" t="s">
+        <v>262</v>
+      </c>
+      <c r="K111" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>110</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H112" t="s">
+        <v>40</v>
+      </c>
+      <c r="I112" t="s">
+        <v>9</v>
+      </c>
+      <c r="J112" t="s">
+        <v>262</v>
+      </c>
+      <c r="K112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>111</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H113" t="s">
+        <v>40</v>
+      </c>
+      <c r="I113" t="s">
+        <v>210</v>
+      </c>
+      <c r="J113" t="s">
+        <v>262</v>
+      </c>
+      <c r="K113" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>112</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>3</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H114" t="s">
+        <v>40</v>
+      </c>
+      <c r="I114" t="s">
+        <v>8</v>
+      </c>
+      <c r="J114" t="s">
+        <v>262</v>
+      </c>
+      <c r="K114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>113</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115">
+        <v>4</v>
+      </c>
+      <c r="E115">
+        <v>3</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="H115" t="s">
+        <v>40</v>
+      </c>
+      <c r="I115" t="s">
+        <v>8</v>
+      </c>
+      <c r="J115" t="s">
+        <v>262</v>
+      </c>
+      <c r="K115" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>114</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="H116" t="s">
+        <v>40</v>
+      </c>
+      <c r="I116" t="s">
+        <v>9</v>
+      </c>
+      <c r="J116" t="s">
+        <v>262</v>
+      </c>
+      <c r="K116" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>115</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H117" t="s">
+        <v>40</v>
+      </c>
+      <c r="I117" t="s">
+        <v>9</v>
+      </c>
+      <c r="J117" t="s">
+        <v>262</v>
+      </c>
+      <c r="K117" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>116</v>
+      </c>
+      <c r="C118">
+        <v>4</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H118" t="s">
+        <v>40</v>
+      </c>
+      <c r="I118" t="s">
+        <v>9</v>
+      </c>
+      <c r="J118" t="s">
+        <v>262</v>
+      </c>
+      <c r="K118" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>117</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119">
+        <v>6</v>
+      </c>
+      <c r="E119">
+        <v>6</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="H119" t="s">
+        <v>40</v>
+      </c>
+      <c r="I119" t="s">
+        <v>8</v>
+      </c>
+      <c r="J119" t="s">
+        <v>262</v>
+      </c>
+      <c r="K119" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>118</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H120" t="s">
+        <v>40</v>
+      </c>
+      <c r="I120" t="s">
+        <v>9</v>
+      </c>
+      <c r="J120" t="s">
+        <v>274</v>
+      </c>
+      <c r="K120" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>119</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H121" t="s">
+        <v>40</v>
+      </c>
+      <c r="I121" t="s">
+        <v>9</v>
+      </c>
+      <c r="J121" t="s">
+        <v>273</v>
+      </c>
+      <c r="K121" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>120</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H122" t="s">
+        <v>40</v>
+      </c>
+      <c r="I122" t="s">
+        <v>210</v>
+      </c>
+      <c r="J122" t="s">
+        <v>273</v>
+      </c>
+      <c r="K122" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>121</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H123" t="s">
+        <v>40</v>
+      </c>
+      <c r="I123" t="s">
+        <v>210</v>
+      </c>
+      <c r="J123" t="s">
+        <v>273</v>
+      </c>
+      <c r="K123" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>122</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H124" t="s">
+        <v>40</v>
+      </c>
+      <c r="I124" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" t="s">
+        <v>273</v>
+      </c>
+      <c r="K124" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>123</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H125" t="s">
+        <v>40</v>
+      </c>
+      <c r="I125" t="s">
+        <v>9</v>
+      </c>
+      <c r="J125" t="s">
+        <v>273</v>
+      </c>
+      <c r="K125" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>124</v>
+      </c>
+      <c r="C126">
+        <v>3</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H126" t="s">
+        <v>40</v>
+      </c>
+      <c r="I126" t="s">
+        <v>9</v>
+      </c>
+      <c r="J126" t="s">
+        <v>273</v>
+      </c>
+      <c r="K126" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>125</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127">
+        <v>2</v>
+      </c>
+      <c r="E127">
+        <v>3</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H127" t="s">
+        <v>40</v>
+      </c>
+      <c r="I127" t="s">
+        <v>8</v>
+      </c>
+      <c r="J127" t="s">
+        <v>273</v>
+      </c>
+      <c r="K127" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>126</v>
+      </c>
+      <c r="C128">
+        <v>4</v>
+      </c>
+      <c r="D128">
+        <v>4</v>
+      </c>
+      <c r="E128">
+        <v>3</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H128" t="s">
+        <v>40</v>
+      </c>
+      <c r="I128" t="s">
+        <v>254</v>
+      </c>
+      <c r="J128" t="s">
+        <v>273</v>
+      </c>
+      <c r="K128" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>127</v>
+      </c>
+      <c r="C129">
+        <v>5</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H129" t="s">
+        <v>40</v>
+      </c>
+      <c r="J129" t="s">
+        <v>273</v>
+      </c>
+      <c r="K129" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
@@ -3589,7 +5427,7 @@
       <formula1>"자연,비전,화염,냉기,신성,암흑,None"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048576">
-      <formula1>"전사,사제,사냥꾼,드루이드,마법사,성기사,도적,주술사,중립"</formula1>
+      <formula1>"전사,사제,사냥꾼,드루이드,마법사,성기사,도적,주술사,중립,흑마법사"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576">
       <formula1>"멀록,야수,None,정령,기계,용족"</formula1>

--- a/ProjectC/Assets/Excel/CardData.xlsx
+++ b/ProjectC/Assets/Excel/CardData.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3562" uniqueCount="1393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3924" uniqueCount="1466">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3938,10 +3938,6 @@
     <t>HasWeapon</t>
   </si>
   <si>
-    <t>HasWeapon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SpellType</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5374,6 +5370,287 @@
   </si>
   <si>
     <t>Windfury</t>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllTargetMinion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Health</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FriendlyHero</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllEnemyTargetExceptSelf</t>
+  </si>
+  <si>
+    <t>AllEnemyTarget</t>
+  </si>
+  <si>
+    <t>AllEnemyTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllFrendlyTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllFrendlyTargetExceptSelf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DrawCard</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taunt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomEnemyMinion</t>
+  </si>
+  <si>
+    <t>SpellAttack</t>
+  </si>
+  <si>
+    <t>SpellAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpellAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrendlyMinions</t>
+  </si>
+  <si>
+    <t>FrendlyMinions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyMinions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManaCase</t>
+  </si>
+  <si>
+    <t>ManaCase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mana</t>
+  </si>
+  <si>
+    <t>Mana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <t>Armor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Freeze</t>
+  </si>
+  <si>
+    <t>AllEnemyMinions</t>
+  </si>
+  <si>
+    <t>AllMinions</t>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Under</t>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyWeapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FriendlyWeapon</t>
+  </si>
+  <si>
+    <t>FriendlyWeapon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Freeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AllTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battlecry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remove</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>악마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battlecry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Battlecry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnSpellCast</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Define</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsDead</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsAttaked</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Turn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnemyWeapon</t>
+  </si>
+  <si>
+    <t>ConditionStat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11082,7 +11359,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -11094,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G142" t="s">
         <v>474</v>
@@ -11123,7 +11400,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -11135,7 +11412,7 @@
         <v>1</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="G143" t="s">
         <v>475</v>
@@ -11164,7 +11441,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -11176,7 +11453,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="G144" t="s">
         <v>476</v>
@@ -11217,7 +11494,7 @@
         <v>4</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G145" t="s">
         <v>477</v>
@@ -11246,7 +11523,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -11258,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="G146" t="s">
         <v>479</v>
@@ -11287,7 +11564,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -11328,7 +11605,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -11369,7 +11646,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="C149">
         <v>2</v>
@@ -11381,7 +11658,7 @@
         <v>3</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="G149" t="s">
         <v>486</v>
@@ -11410,7 +11687,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -11422,7 +11699,7 @@
         <v>3</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="G150" t="s">
         <v>487</v>
@@ -11451,7 +11728,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C151">
         <v>2</v>
@@ -11489,7 +11766,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -11527,7 +11804,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C153">
         <v>3</v>
@@ -11565,7 +11842,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="C154">
         <v>2</v>
@@ -11603,7 +11880,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -11641,7 +11918,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C156">
         <v>2</v>
@@ -11717,7 +11994,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C158">
         <v>3</v>
@@ -11755,7 +12032,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C159">
         <v>3</v>
@@ -11793,7 +12070,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C160">
         <v>3</v>
@@ -11831,7 +12108,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -11869,7 +12146,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C162">
         <v>3</v>
@@ -11910,7 +12187,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C163">
         <v>3</v>
@@ -11948,7 +12225,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C164">
         <v>3</v>
@@ -11986,7 +12263,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="C165">
         <v>3</v>
@@ -12024,7 +12301,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C166">
         <v>3</v>
@@ -12065,7 +12342,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C167">
         <v>4</v>
@@ -12103,7 +12380,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C168">
         <v>4</v>
@@ -12141,7 +12418,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C169">
         <v>4</v>
@@ -12179,7 +12456,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C170">
         <v>4</v>
@@ -12191,7 +12468,7 @@
         <v>3</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G170" t="s">
         <v>516</v>
@@ -12220,7 +12497,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C171">
         <v>4</v>
@@ -12232,7 +12509,7 @@
         <v>7</v>
       </c>
       <c r="F171" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G171" t="s">
         <v>517</v>
@@ -12261,7 +12538,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C172">
         <v>4</v>
@@ -12302,7 +12579,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C173">
         <v>4</v>
@@ -12340,7 +12617,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -12378,7 +12655,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -12416,7 +12693,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -12454,7 +12731,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -12492,7 +12769,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -12533,7 +12810,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -12571,7 +12848,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="C180">
         <v>6</v>
@@ -12609,7 +12886,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="C181">
         <v>6</v>
@@ -12647,7 +12924,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C182">
         <v>6</v>
@@ -12688,7 +12965,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -12726,7 +13003,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -12764,7 +13041,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -12802,7 +13079,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -12878,7 +13155,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C188">
         <v>1</v>
@@ -12916,7 +13193,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C189">
         <v>2</v>
@@ -12954,7 +13231,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C190">
         <v>2</v>
@@ -12992,7 +13269,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C191">
         <v>2</v>
@@ -13068,7 +13345,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C193">
         <v>2</v>
@@ -13106,7 +13383,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C194">
         <v>2</v>
@@ -13144,7 +13421,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="C195">
         <v>2</v>
@@ -13182,7 +13459,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="C196">
         <v>2</v>
@@ -13220,7 +13497,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C197">
         <v>2</v>
@@ -13258,7 +13535,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="C198">
         <v>3</v>
@@ -13296,7 +13573,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C199">
         <v>3</v>
@@ -13334,7 +13611,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="C200">
         <v>3</v>
@@ -13372,7 +13649,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="C201">
         <v>3</v>
@@ -13410,7 +13687,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C202">
         <v>3</v>
@@ -13448,7 +13725,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C203">
         <v>3</v>
@@ -13486,7 +13763,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="C204">
         <v>3</v>
@@ -13562,7 +13839,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="C206">
         <v>3</v>
@@ -13600,7 +13877,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C207">
         <v>3</v>
@@ -13638,7 +13915,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="C208">
         <v>3</v>
@@ -13676,7 +13953,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -13714,7 +13991,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -13752,7 +14029,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -13790,7 +14067,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -13828,7 +14105,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -13866,7 +14143,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="C214">
         <v>5</v>
@@ -13904,7 +14181,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C215">
         <v>5</v>
@@ -13942,7 +14219,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="C216">
         <v>5</v>
@@ -13980,7 +14257,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="C217">
         <v>5</v>
@@ -14018,7 +14295,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C218">
         <v>6</v>
@@ -14056,7 +14333,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="C219">
         <v>6</v>
@@ -14094,7 +14371,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C220">
         <v>7</v>
@@ -14132,7 +14409,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -14170,7 +14447,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -14208,7 +14485,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -14246,7 +14523,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C224">
         <v>3</v>
@@ -14284,7 +14561,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C225">
         <v>3</v>
@@ -14322,7 +14599,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="C226">
         <v>3</v>
@@ -14360,7 +14637,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C227">
         <v>3</v>
@@ -14398,7 +14675,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C228">
         <v>5</v>
@@ -14436,7 +14713,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="C229">
         <v>10</v>
@@ -14474,7 +14751,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C230">
         <v>12</v>
@@ -14512,7 +14789,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="C231">
         <v>20</v>
@@ -14550,7 +14827,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="C232">
         <v>2</v>
@@ -14588,7 +14865,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="C233">
         <v>2</v>
@@ -14626,7 +14903,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C234">
         <v>2</v>
@@ -14664,7 +14941,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C235">
         <v>2</v>
@@ -14702,7 +14979,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="C236">
         <v>3</v>
@@ -14740,7 +15017,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -14772,7 +15049,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C238">
         <v>3</v>
@@ -14848,7 +15125,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C240">
         <v>5</v>
@@ -14886,7 +15163,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C241">
         <v>4</v>
@@ -14924,7 +15201,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C242">
         <v>4</v>
@@ -14962,7 +15239,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="C243">
         <v>5</v>
@@ -15000,7 +15277,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="C244">
         <v>5</v>
@@ -15038,7 +15315,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -15076,7 +15353,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C246">
         <v>4</v>
@@ -15108,7 +15385,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C247">
         <v>4</v>
@@ -15140,7 +15417,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C248">
         <v>5</v>
@@ -15178,7 +15455,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="C249">
         <v>6</v>
@@ -15216,7 +15493,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="C250">
         <v>4</v>
@@ -15254,7 +15531,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C251">
         <v>6</v>
@@ -15330,7 +15607,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -15368,7 +15645,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -15406,7 +15683,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -15444,7 +15721,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -15482,7 +15759,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C257">
         <v>6</v>
@@ -15520,7 +15797,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C258">
         <v>6</v>
@@ -15558,7 +15835,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -15596,7 +15873,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C260">
         <v>6</v>
@@ -15634,7 +15911,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C261">
         <v>6</v>
@@ -15672,7 +15949,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C262">
         <v>3</v>
@@ -15710,7 +15987,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C263">
         <v>6</v>
@@ -15748,7 +16025,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C264">
         <v>7</v>
@@ -15786,7 +16063,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C265">
         <v>8</v>
@@ -15824,7 +16101,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C266">
         <v>8</v>
@@ -15862,7 +16139,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C267">
         <v>9</v>
@@ -15900,7 +16177,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C268">
         <v>9</v>
@@ -15938,7 +16215,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="C269">
         <v>9</v>
@@ -15976,7 +16253,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="C270">
         <v>9</v>
@@ -16154,7 +16431,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C275">
         <v>2</v>
@@ -16396,7 +16673,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="C282">
         <v>2</v>
@@ -16431,7 +16708,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="C283">
         <v>2</v>
@@ -16463,7 +16740,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C284">
         <v>2</v>
@@ -16495,7 +16772,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C285">
         <v>2</v>
@@ -16527,7 +16804,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C286">
         <v>2</v>
@@ -16565,7 +16842,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C287">
         <v>3</v>
@@ -16597,7 +16874,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -16629,7 +16906,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -16661,7 +16938,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C290">
         <v>4</v>
@@ -16693,7 +16970,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -16731,7 +17008,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C292">
         <v>5</v>
@@ -16769,7 +17046,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -16801,7 +17078,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -16833,7 +17110,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C295">
         <v>5</v>
@@ -16874,7 +17151,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C296">
         <v>5</v>
@@ -16915,7 +17192,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -16947,7 +17224,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C298">
         <v>4</v>
@@ -16979,7 +17256,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="C299">
         <v>4</v>
@@ -17017,7 +17294,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="C300">
         <v>4</v>
@@ -17049,7 +17326,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C301">
         <v>4</v>
@@ -17113,7 +17390,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="C303">
         <v>5</v>
@@ -17145,7 +17422,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="C304">
         <v>5</v>
@@ -17209,7 +17486,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C306">
         <v>5</v>
@@ -17241,7 +17518,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C307">
         <v>5</v>
@@ -17273,7 +17550,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C308">
         <v>6</v>
@@ -17305,7 +17582,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -17346,7 +17623,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="C310">
         <v>7</v>
@@ -17358,7 +17635,7 @@
         <v>5</v>
       </c>
       <c r="G310" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="H310" t="s">
         <v>590</v>
@@ -17384,7 +17661,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="C311">
         <v>7</v>
@@ -17416,7 +17693,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="C312">
         <v>7</v>
@@ -17448,7 +17725,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C313">
         <v>7</v>
@@ -17486,7 +17763,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C314">
         <v>7</v>
@@ -17515,7 +17792,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C315">
         <v>7</v>
@@ -17544,7 +17821,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="C316">
         <v>9</v>
@@ -17582,13 +17859,13 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="C317">
         <v>9</v>
       </c>
       <c r="G317" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="H317" t="s">
         <v>739</v>
@@ -17611,7 +17888,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="C318">
         <v>9</v>
@@ -17640,7 +17917,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C319">
         <v>2</v>
@@ -17672,7 +17949,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="C320">
         <v>2</v>
@@ -17704,7 +17981,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C321">
         <v>2</v>
@@ -17742,7 +18019,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C322">
         <v>2</v>
@@ -17774,7 +18051,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="C323">
         <v>3</v>
@@ -17806,7 +18083,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="C324">
         <v>3</v>
@@ -17838,7 +18115,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -17870,7 +18147,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C326">
         <v>2</v>
@@ -17902,7 +18179,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C327">
         <v>3</v>
@@ -17937,7 +18214,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C328">
         <v>5</v>
@@ -18007,7 +18284,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -18039,7 +18316,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C331">
         <v>2</v>
@@ -18071,7 +18348,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="C332">
         <v>7</v>
@@ -18384,7 +18661,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -18416,7 +18693,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -18454,7 +18731,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C342">
         <v>2</v>
@@ -18492,7 +18769,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C343">
         <v>3</v>
@@ -18524,7 +18801,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C344">
         <v>3</v>
@@ -18556,7 +18833,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="C345">
         <v>4</v>
@@ -18588,7 +18865,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C346">
         <v>3</v>
@@ -18620,7 +18897,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C347">
         <v>3</v>
@@ -18658,7 +18935,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C348">
         <v>3</v>
@@ -18690,7 +18967,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C349">
         <v>4</v>
@@ -18728,7 +19005,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C350">
         <v>6</v>
@@ -18760,7 +19037,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C351">
         <v>3</v>
@@ -18792,7 +19069,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C352">
         <v>3</v>
@@ -18824,7 +19101,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C353">
         <v>10</v>
@@ -18856,7 +19133,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C354">
         <v>7</v>
@@ -18894,7 +19171,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -18932,7 +19209,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -18964,7 +19241,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -18996,7 +19273,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C358">
         <v>1</v>
@@ -19028,7 +19305,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -19060,7 +19337,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C360">
         <v>1</v>
@@ -19092,7 +19369,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C361">
         <v>2</v>
@@ -19130,7 +19407,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C362">
         <v>2</v>
@@ -19162,7 +19439,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C363">
         <v>3</v>
@@ -19200,7 +19477,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C364">
         <v>3</v>
@@ -19232,7 +19509,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C365">
         <v>5</v>
@@ -19264,7 +19541,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="C366">
         <v>5</v>
@@ -19296,7 +19573,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C367">
         <v>3</v>
@@ -19331,7 +19608,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C368">
         <v>6</v>
@@ -19363,7 +19640,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C369">
         <v>8</v>
@@ -19395,7 +19672,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C370">
         <v>8</v>
@@ -19433,7 +19710,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C371">
         <v>5</v>
@@ -19468,7 +19745,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C372">
         <v>1</v>
@@ -19506,7 +19783,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -19538,7 +19815,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -19570,7 +19847,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C375">
         <v>1</v>
@@ -19602,7 +19879,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="C376">
         <v>1</v>
@@ -19640,7 +19917,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C377">
         <v>2</v>
@@ -19672,7 +19949,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C378">
         <v>2</v>
@@ -19704,7 +19981,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C379">
         <v>3</v>
@@ -19736,7 +20013,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C380">
         <v>4</v>
@@ -19774,7 +20051,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C381">
         <v>6</v>
@@ -19812,7 +20089,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C382">
         <v>2</v>
@@ -19850,7 +20127,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C383">
         <v>4</v>
@@ -19888,7 +20165,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C384">
         <v>4</v>
@@ -19920,7 +20197,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C385">
         <v>4</v>
@@ -19952,7 +20229,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C386">
         <v>6</v>
@@ -19984,7 +20261,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C387">
         <v>3</v>
@@ -20016,7 +20293,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C388">
         <v>4</v>
@@ -20048,7 +20325,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C389">
         <v>6</v>
@@ -20086,7 +20363,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C390">
         <v>7</v>
@@ -20124,7 +20401,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -20162,7 +20439,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -20194,7 +20471,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C393">
         <v>1</v>
@@ -20226,7 +20503,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C394">
         <v>1</v>
@@ -20258,7 +20535,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C395">
         <v>2</v>
@@ -20290,7 +20567,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="C396">
         <v>2</v>
@@ -20328,7 +20605,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C397">
         <v>2</v>
@@ -20392,7 +20669,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C399">
         <v>2</v>
@@ -20424,7 +20701,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C400">
         <v>3</v>
@@ -20456,7 +20733,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="C401">
         <v>3</v>
@@ -20491,7 +20768,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="C402">
         <v>3</v>
@@ -20529,7 +20806,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C403">
         <v>4</v>
@@ -20567,7 +20844,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -20599,7 +20876,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C405">
         <v>2</v>
@@ -20637,7 +20914,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C406">
         <v>6</v>
@@ -20675,7 +20952,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="C407">
         <v>3</v>
@@ -20713,7 +20990,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="C408">
         <v>1</v>
@@ -20751,7 +21028,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C409">
         <v>1</v>
@@ -20789,7 +21066,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -20821,7 +21098,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -20853,7 +21130,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C412">
         <v>1</v>
@@ -20885,7 +21162,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C413">
         <v>2</v>
@@ -20920,7 +21197,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="C414">
         <v>3</v>
@@ -20958,7 +21235,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C415">
         <v>2</v>
@@ -20990,7 +21267,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C416">
         <v>3</v>
@@ -21022,7 +21299,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="C417">
         <v>3</v>
@@ -21054,7 +21331,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C418">
         <v>3</v>
@@ -21086,7 +21363,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C419">
         <v>3</v>
@@ -21124,7 +21401,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C420">
         <v>3</v>
@@ -21156,7 +21433,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C421">
         <v>5</v>
@@ -21191,7 +21468,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C422">
         <v>5</v>
@@ -21229,7 +21506,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C423">
         <v>8</v>
@@ -21267,7 +21544,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="C424">
         <v>2</v>
@@ -21308,7 +21585,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C425">
         <v>1</v>
@@ -21346,7 +21623,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C426">
         <v>1</v>
@@ -21384,7 +21661,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="C427">
         <v>1</v>
@@ -21416,7 +21693,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C428">
         <v>2</v>
@@ -21448,7 +21725,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C429">
         <v>3</v>
@@ -21480,7 +21757,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C430">
         <v>4</v>
@@ -21518,7 +21795,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C431">
         <v>3</v>
@@ -21556,7 +21833,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="C432">
         <v>3</v>
@@ -21594,7 +21871,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="C433">
         <v>4</v>
@@ -21626,7 +21903,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="C434">
         <v>5</v>
@@ -21664,7 +21941,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C435">
         <v>6</v>
@@ -21696,7 +21973,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="C436">
         <v>4</v>
@@ -21734,7 +22011,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C437">
         <v>5</v>
@@ -21766,7 +22043,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C438">
         <v>8</v>
@@ -21798,7 +22075,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C439">
         <v>9</v>
@@ -21836,7 +22113,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C440">
         <v>1</v>
@@ -21874,7 +22151,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C441">
         <v>3</v>
@@ -21909,7 +22186,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C442">
         <v>6</v>
@@ -21947,7 +22224,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C443">
         <v>0</v>
@@ -21979,7 +22256,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C444">
         <v>2</v>
@@ -22011,7 +22288,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C445">
         <v>2</v>
@@ -22049,7 +22326,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C446">
         <v>2</v>
@@ -22081,7 +22358,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C447">
         <v>2</v>
@@ -22113,7 +22390,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C448">
         <v>4</v>
@@ -22151,7 +22428,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C449">
         <v>1</v>
@@ -22183,7 +22460,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C450">
         <v>2</v>
@@ -22221,7 +22498,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C451">
         <v>2</v>
@@ -22253,7 +22530,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C452">
         <v>3</v>
@@ -22291,7 +22568,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C453">
         <v>4</v>
@@ -22323,7 +22600,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C454">
         <v>1</v>
@@ -22355,7 +22632,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="C455">
         <v>5</v>
@@ -22387,7 +22664,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="C456">
         <v>7</v>
@@ -22422,7 +22699,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="C457">
         <v>8</v>
@@ -22460,7 +22737,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -22495,7 +22772,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="C459">
         <v>1</v>
@@ -22557,7 +22834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L158"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.625" customWidth="1"/>
@@ -22567,12 +22844,13 @@
     <col min="8" max="8" width="16.625" customWidth="1"/>
     <col min="9" max="9" width="20.75" customWidth="1"/>
     <col min="10" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="12.75" customWidth="1"/>
+    <col min="12" max="12" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>1463</v>
       </c>
       <c r="B1" t="s">
         <v>987</v>
@@ -22599,13 +22877,13 @@
         <v>1007</v>
       </c>
       <c r="J1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="K1" t="s">
-        <v>1356</v>
+        <v>1364</v>
       </c>
       <c r="L1" t="s">
-        <v>1365</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -22619,7 +22897,7 @@
         <v>1005</v>
       </c>
       <c r="D2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -22644,7 +22922,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1004</v>
+        <v>1464</v>
       </c>
       <c r="C4" t="s">
         <v>999</v>
@@ -22667,7 +22945,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="D5" t="s">
         <v>998</v>
@@ -22684,7 +22962,7 @@
         <v>1025</v>
       </c>
       <c r="D6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -22701,10 +22979,10 @@
         <v>991</v>
       </c>
       <c r="C7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D7" t="s">
-        <v>1003</v>
+        <v>1461</v>
       </c>
       <c r="G7" t="s">
         <v>1032</v>
@@ -22715,10 +22993,10 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D8" t="s">
         <v>1366</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -22726,21 +23004,21 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D9" t="s">
         <v>1368</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>995</v>
+        <v>1413</v>
       </c>
       <c r="D10" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -22748,16 +23026,16 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>1371</v>
+        <v>991</v>
       </c>
       <c r="C11" t="s">
-        <v>1370</v>
+        <v>1027</v>
       </c>
       <c r="D11" t="s">
-        <v>1039</v>
+        <v>998</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -22765,27 +23043,30 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>991</v>
       </c>
       <c r="C12" t="s">
-        <v>1368</v>
+        <v>995</v>
       </c>
       <c r="D12" t="s">
-        <v>998</v>
+        <v>1008</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1372</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>999</v>
+        <v>1413</v>
       </c>
       <c r="D13" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -22793,354 +23074,2312 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="C14" t="s">
-        <v>999</v>
+        <v>1369</v>
       </c>
       <c r="D14" t="s">
-        <v>1010</v>
+        <v>1038</v>
       </c>
       <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="J14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1373</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>1028</v>
+        <v>1367</v>
       </c>
       <c r="D15" t="s">
-        <v>1374</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
+        <v>998</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C16" t="s">
+        <v>999</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C17" t="s">
+        <v>999</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C19" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D19" t="s">
         <v>1368</v>
       </c>
-      <c r="D16" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="C20" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>991</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D21" t="s">
+        <v>998</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B22" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D22" t="s">
         <v>1375</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1415</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D24" t="s">
         <v>1376</v>
       </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>28</v>
-      </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>29</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D25" t="s">
         <v>1368</v>
       </c>
-      <c r="D19" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>29</v>
-      </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s">
         <v>1378</v>
       </c>
-      <c r="D20" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>30</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>31</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C27" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D27" t="s">
         <v>1379</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1380</v>
-      </c>
-      <c r="E22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C23" t="s">
-        <v>999</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1383</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="s">
-        <v>1385</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1382</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1384</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>991</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1039</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>140</v>
+        <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>1371</v>
+        <v>1380</v>
       </c>
       <c r="C28" t="s">
-        <v>1388</v>
+        <v>999</v>
       </c>
       <c r="D28" t="s">
-        <v>1355</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1382</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>141</v>
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1381</v>
       </c>
       <c r="C29" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D29" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>1383</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>992</v>
+        <v>1022</v>
       </c>
       <c r="C30" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C31" t="s">
         <v>1005</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>1003</v>
       </c>
-      <c r="E30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>143</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E31">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
         <v>991</v>
       </c>
       <c r="C32" t="s">
-        <v>1389</v>
+        <v>1005</v>
       </c>
       <c r="D32" t="s">
-        <v>1369</v>
-      </c>
-      <c r="G32" t="s">
-        <v>1032</v>
+        <v>1038</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>1390</v>
+        <v>1413</v>
       </c>
       <c r="D33" t="s">
-        <v>1391</v>
+        <v>998</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="C34" t="s">
-        <v>1392</v>
+        <v>997</v>
       </c>
       <c r="D34" t="s">
-        <v>1369</v>
+        <v>998</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>99</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1002</v>
+        <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>1005</v>
+        <v>1359</v>
       </c>
       <c r="D35" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="J35" t="b">
-        <v>1</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C36" t="s">
+        <v>999</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>46</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C42" t="s">
+        <v>997</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>49</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>49</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E45">
+        <v>8</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>51</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>51</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>52</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>53</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>53</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>54</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>54</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>55</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>56</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>57</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E55">
+        <v>2</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>58</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I56" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>59</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>60</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D59" t="s">
+        <v>998</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>991</v>
+      </c>
+      <c r="C62" t="s">
+        <v>997</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I62" t="s">
+        <v>197</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>63</v>
+      </c>
+      <c r="B63" t="s">
+        <v>991</v>
+      </c>
+      <c r="C63" t="s">
+        <v>999</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E63">
+        <v>2</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I63" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>991</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I64" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C66" t="s">
+        <v>995</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I66" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I67" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D68" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C69" t="s">
+        <v>999</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="C70" t="s">
+        <v>997</v>
+      </c>
+      <c r="D70" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>997</v>
+      </c>
+      <c r="D72" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E75">
+        <v>3</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C77" t="s">
+        <v>995</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D78" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C82" t="s">
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C84" t="s">
+        <v>999</v>
+      </c>
+      <c r="D84" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C85" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E87">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C88" t="s">
+        <v>999</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E88">
+        <v>4</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C89" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C90" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>88</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C91" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>89</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D93" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C94" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D94" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="C95" t="s">
+        <v>997</v>
+      </c>
+      <c r="D95" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>91</v>
+      </c>
+      <c r="B96" t="s">
+        <v>991</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>92</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C97" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>93</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>94</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E99">
+        <v>2</v>
+      </c>
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>94</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C100" t="s">
+        <v>995</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>95</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H101">
+        <v>3</v>
+      </c>
+      <c r="J101" t="b">
+        <v>1</v>
+      </c>
+      <c r="L101" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>96</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H102">
+        <v>5</v>
+      </c>
+      <c r="L102" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>97</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>97</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>98</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>99</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E106">
+        <v>2</v>
+      </c>
+      <c r="J106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>100</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C107" t="s">
+        <v>999</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108">
         <v>101</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B108" t="s">
         <v>1002</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C108" t="s">
         <v>1005</v>
       </c>
-      <c r="D36" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E36">
+      <c r="D108" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E108">
         <v>3</v>
       </c>
-      <c r="J36" t="b">
-        <v>1</v>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>102</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E109">
+        <v>1</v>
+      </c>
+      <c r="J109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>102</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>103</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1395</v>
+      </c>
+      <c r="J111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>104</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>104</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>106</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>107</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E115">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>108</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>108</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>109</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I118" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>110</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="J119" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>110</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>111</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C121" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
+      </c>
+      <c r="K121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>112</v>
+      </c>
+      <c r="C122" t="s">
+        <v>999</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>113</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C123" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>114</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1002</v>
+      </c>
+      <c r="J124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>115</v>
+      </c>
+      <c r="C125" t="s">
+        <v>997</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>116</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>117</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E127">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>118</v>
+      </c>
+      <c r="B128" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E128">
+        <v>3</v>
+      </c>
+      <c r="J128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>119</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G129" t="s">
+        <v>1446</v>
+      </c>
+      <c r="I129" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>119</v>
+      </c>
+      <c r="B130" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C130" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E130">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>120</v>
+      </c>
+      <c r="B131" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C131" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E131">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>120</v>
+      </c>
+      <c r="B132" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>121</v>
+      </c>
+      <c r="B133" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C133" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1354</v>
+      </c>
+      <c r="J133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>122</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>122</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C135" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>123</v>
+      </c>
+      <c r="C136" t="s">
+        <v>997</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>124</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>125</v>
+      </c>
+      <c r="B138" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E138">
+        <v>2</v>
+      </c>
+      <c r="J138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>125</v>
+      </c>
+      <c r="B139" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>126</v>
+      </c>
+      <c r="B140" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E140">
+        <v>4</v>
+      </c>
+      <c r="J140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>127</v>
+      </c>
+      <c r="B141" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D141" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E141">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>128</v>
+      </c>
+      <c r="B142" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D142" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>128</v>
+      </c>
+      <c r="B143" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>129</v>
+      </c>
+      <c r="B144" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D144" t="s">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>130</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C145" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>131</v>
+      </c>
+      <c r="B146" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>133</v>
+      </c>
+      <c r="B147" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C147" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D147" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>134</v>
+      </c>
+      <c r="B148" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C148" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D148" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>135</v>
+      </c>
+      <c r="B149" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D149" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E149">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>136</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D150" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G150" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H150">
+        <v>3</v>
+      </c>
+      <c r="L150" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>137</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D151" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>140</v>
+      </c>
+      <c r="B152" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D152" t="s">
+        <v>1354</v>
+      </c>
+      <c r="K152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>141</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D153" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>142</v>
+      </c>
+      <c r="B154" t="s">
+        <v>992</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D154" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>143</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D155" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>144</v>
+      </c>
+      <c r="B156" t="s">
+        <v>991</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D156" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G156" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>145</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>146</v>
+      </c>
+      <c r="C158" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D158" t="s">
+        <v>1368</v>
       </c>
     </row>
   </sheetData>
+  <dataConsolidate/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -23149,45 +25388,45 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>List!$D$2:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>G10:G29 G1:G7 G32:G36 G39:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
             <xm:f>List!$E$2:$E$11</xm:f>
           </x14:formula1>
-          <xm:sqref>I10:I29 I1:I7 I32:I36 I39:I1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>List!$C$2:$C$26</xm:f>
-          </x14:formula1>
-          <xm:sqref>D1:D36 D39:D1048576</xm:sqref>
+          <xm:sqref>I1:I7 I156:I1048576 I12:I33 I45:I101 I104:I153</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>List!$J$2:$J$3</xm:f>
           </x14:formula1>
-          <xm:sqref>L1:L7 J10:J29 J1:J7 L10:L36 L39:L1048576 J32:J36 J39:J1048576</xm:sqref>
+          <xm:sqref>K1:K7 K12:K33 K45:K101 J1:J101 K104:K1048576 J104:J1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>List!$C$2:$C$32</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:D1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>List!$B$2:$B$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>List!$A$2:$A$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>B1:B1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>List!$D$2:$D$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G1:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>List!$K$2:$K$4</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K29 K1:K7 K32:K36 K39:K1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>List!$B$2:$B$14</xm:f>
-          </x14:formula1>
-          <xm:sqref>C1:C36 C39:C1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>List!$A$2:$A$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>B1:B36 B39:B1048576</xm:sqref>
+          <xm:sqref>L1:L1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -23197,7 +25436,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
@@ -23241,10 +25480,10 @@
         <v>10</v>
       </c>
       <c r="J1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="K1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -23255,7 +25494,7 @@
         <v>1005</v>
       </c>
       <c r="C2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D2" t="s">
         <v>1029</v>
@@ -23279,7 +25518,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -23296,7 +25535,7 @@
         <v>1030</v>
       </c>
       <c r="E3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F3" t="s">
         <v>202</v>
@@ -23314,7 +25553,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -23325,7 +25564,7 @@
         <v>997</v>
       </c>
       <c r="C4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D4" t="s">
         <v>1031</v>
@@ -23346,7 +25585,7 @@
         <v>310</v>
       </c>
       <c r="K4" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -23357,7 +25596,7 @@
         <v>1026</v>
       </c>
       <c r="C5" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D5" t="s">
         <v>1033</v>
@@ -23375,7 +25614,7 @@
         <v>307</v>
       </c>
       <c r="I5" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -23386,10 +25625,10 @@
         <v>1027</v>
       </c>
       <c r="C6" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D6" t="s">
-        <v>1034</v>
+        <v>1417</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
@@ -23412,7 +25651,10 @@
         <v>995</v>
       </c>
       <c r="C7" t="s">
-        <v>1049</v>
+        <v>1048</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1418</v>
       </c>
       <c r="E7" t="s">
         <v>200</v>
@@ -23432,7 +25674,10 @@
         <v>999</v>
       </c>
       <c r="C8" t="s">
-        <v>1046</v>
+        <v>1045</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1425</v>
       </c>
       <c r="E8" t="s">
         <v>411</v>
@@ -23452,7 +25697,10 @@
         <v>1028</v>
       </c>
       <c r="C9" t="s">
-        <v>1047</v>
+        <v>1046</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1457</v>
       </c>
       <c r="E9" t="s">
         <v>435</v>
@@ -23463,16 +25711,19 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B10" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C10" t="s">
-        <v>1050</v>
+        <v>1049</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1458</v>
       </c>
       <c r="E10" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H10" t="s">
         <v>469</v>
@@ -23480,32 +25731,41 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B11" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="C11" t="s">
-        <v>1041</v>
+        <v>1040</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1459</v>
       </c>
       <c r="E11" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H11" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1465</v>
+      </c>
       <c r="B12" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="C12" t="s">
         <v>1008</v>
       </c>
+      <c r="D12" t="s">
+        <v>1460</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="C13" t="s">
         <v>1003</v>
@@ -23513,70 +25773,112 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="C14" t="s">
         <v>1009</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
+        <v>1414</v>
+      </c>
       <c r="C15" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>1420</v>
+      </c>
       <c r="C16" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>1422</v>
+      </c>
       <c r="C17" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>1424</v>
+      </c>
       <c r="C18" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
         <v>998</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>1436</v>
       </c>
     </row>
   </sheetData>
